--- a/testing/testing.xlsx
+++ b/testing/testing.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="49" documentId="8_{DDB18C92-5515-4B9F-B346-B109A66A0069}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C9790F92-D091-435D-964A-F73DF8726E09}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{F3BB62F5-D6B4-4DCF-B071-4DB45C9997CB}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{F3BB62F5-D6B4-4DCF-B071-4DB45C9997CB}"/>
   </bookViews>
   <sheets>
     <sheet name="GT" sheetId="1" r:id="rId1"/>
